--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/4414-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/4414-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{105C5967-450B-43CC-AADE-067AF33B3BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{95B7D124-CE7A-4D81-BDB4-E317B5799B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{15240730-770A-4F18-A164-302F4DCCCBC3}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{53E81A29-FC01-41D5-8A81-32A2A9F851D8}"/>
   </bookViews>
   <sheets>
     <sheet name="4414-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1466,21 +1466,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29EFB7CC-0E79-4540-A1AC-1BBE5A81CCBB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AECB453F-3E45-4953-A24D-FE05223D02D6}">
   <dimension ref="A1:R48"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="5.109375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.6640625" customWidth="1"/>
+    <col min="1" max="2" width="6.5" customWidth="1"/>
+    <col min="3" max="3" width="10.875" customWidth="1"/>
+    <col min="4" max="6" width="10.125" customWidth="1"/>
+    <col min="7" max="7" width="10.625" customWidth="1"/>
+    <col min="8" max="8" width="10.125" customWidth="1"/>
+    <col min="9" max="10" width="10.625" customWidth="1"/>
+    <col min="11" max="17" width="10.125" customWidth="1"/>
+    <col min="18" max="18" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1508,7 +1508,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1538,7 +1538,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1634,7 +1634,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2025</v>
       </c>
@@ -1688,7 +1688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1744,7 +1744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="40">
         <v>2024</v>
       </c>
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1910,7 +1910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="38">
         <v>2023</v>
       </c>
@@ -1964,7 +1964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
@@ -2020,7 +2020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2076,7 +2076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="40">
         <v>2022</v>
       </c>
@@ -2130,7 +2130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>26</v>
       </c>
@@ -2186,7 +2186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>26</v>
       </c>
@@ -2242,7 +2242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="38">
         <v>2021</v>
       </c>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>26</v>
       </c>
@@ -2352,7 +2352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
@@ -2408,7 +2408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="40">
         <v>2020</v>
       </c>
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>26</v>
       </c>
@@ -2518,7 +2518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>26</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="38">
         <v>2019</v>
       </c>
@@ -2628,7 +2628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>26</v>
       </c>
@@ -2684,7 +2684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>26</v>
       </c>
@@ -2740,7 +2740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="40">
         <v>2018</v>
       </c>
@@ -2794,7 +2794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="38">
         <v>2017</v>
       </c>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="40">
         <v>2016</v>
       </c>
@@ -2902,7 +2902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="38">
         <v>2015</v>
       </c>
@@ -2956,7 +2956,7 @@
         <v>2.44</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="40">
         <v>2014</v>
       </c>
@@ -3010,7 +3010,7 @@
         <v>2.83</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="38">
         <v>2013</v>
       </c>
@@ -3064,7 +3064,7 @@
         <v>3.97</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="40">
         <v>2012</v>
       </c>
@@ -3118,7 +3118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="38">
         <v>2011</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="40">
         <v>2010</v>
       </c>
@@ -3226,7 +3226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="38">
         <v>2009</v>
       </c>
@@ -3280,7 +3280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="40">
         <v>2008</v>
       </c>
@@ -3334,7 +3334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="38">
         <v>2007</v>
       </c>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="40">
         <v>2006</v>
       </c>
@@ -3442,7 +3442,7 @@
         <v>2.99</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="38">
         <v>2005</v>
       </c>
@@ -3496,7 +3496,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="40">
         <v>2004</v>
       </c>
@@ -3550,7 +3550,7 @@
         <v>9.02</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="38">
         <v>2003</v>
       </c>
@@ -3604,7 +3604,7 @@
         <v>9.49</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="40">
         <v>2002</v>
       </c>
@@ -3658,7 +3658,7 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="38">
         <v>2001</v>
       </c>
@@ -3712,7 +3712,7 @@
         <v>7.87</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="40">
         <v>2000</v>
       </c>
@@ -3766,7 +3766,7 @@
         <v>5.33</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="38">
         <v>1999</v>
       </c>
@@ -3820,7 +3820,7 @@
         <v>5.82</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="40">
         <v>1998</v>
       </c>
@@ -3874,7 +3874,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="38">
         <v>1997</v>
       </c>
@@ -3928,7 +3928,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="40">
         <v>1996</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="38" t="s">
         <v>40</v>
       </c>
